--- a/data/trans_camb/P16A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,12</t>
+          <t>-2,42; 2,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,55</t>
+          <t>-1,56; 3,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,72</t>
+          <t>-1,81; 2,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,82</t>
+          <t>-3,11; 2,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,49</t>
+          <t>-3,57; 2,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,62</t>
+          <t>-3,41; 1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,17</t>
+          <t>-2,03; 1,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,21</t>
+          <t>-1,49; 2,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,49</t>
+          <t>-1,69; 1,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 148,86</t>
+          <t>-59,11; 133,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 175,24</t>
+          <t>-37,75; 175,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 128,84</t>
+          <t>-40,63; 131,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,7; 145,09</t>
+          <t>-64,8; 122,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,07; 139,93</t>
+          <t>-66,86; 117,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 81,75</t>
+          <t>-60,73; 79,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 98,29</t>
+          <t>-49,27; 74,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 93,74</t>
+          <t>-35,29; 89,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,57; 58,57</t>
+          <t>-39,45; 67,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,1</t>
+          <t>0,13; 5,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,22</t>
+          <t>-0,58; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,74</t>
+          <t>-0,32; 3,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,55</t>
+          <t>-1,55; 4,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,0</t>
+          <t>-2,61; 3,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,9</t>
+          <t>-0,68; 4,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,04</t>
+          <t>-0,2; 3,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,79</t>
+          <t>-1,01; 2,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,6</t>
+          <t>0,18; 3,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 775,13</t>
+          <t>-21,46; 863,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 539,54</t>
+          <t>-31,74; 596,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 587,48</t>
+          <t>-21,02; 780,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 167,13</t>
+          <t>-31,91; 175,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 112,64</t>
+          <t>-52,42; 116,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 204,69</t>
+          <t>-15,71; 179,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 202,43</t>
+          <t>-10,19; 197,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 141,22</t>
+          <t>-29,98; 134,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 187,53</t>
+          <t>2,55; 202,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,62</t>
+          <t>-0,07; 4,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,28</t>
+          <t>-1,42; 2,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,8</t>
+          <t>-1,71; 4,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 9,35</t>
+          <t>-0,38; 9,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,88</t>
+          <t>-1,05; 10,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,8</t>
+          <t>0,82; 10,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,36</t>
+          <t>0,96; 5,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,24</t>
+          <t>-0,76; 3,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,28</t>
+          <t>-1,22; 5,37</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 268,54</t>
+          <t>-5,9; 271,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 136,07</t>
+          <t>-44,34; 140,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 231,36</t>
+          <t>-50,92; 219,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 346,82</t>
+          <t>-12,33; 405,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 399,1</t>
+          <t>-22,75; 426,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,32; 466,35</t>
+          <t>4,27; 441,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,45; 232,29</t>
+          <t>23,69; 240,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 140,01</t>
+          <t>-20,37; 136,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 209,94</t>
+          <t>-30,89; 212,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,89</t>
+          <t>-0,86; 1,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,75</t>
+          <t>-0,29; 2,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,39</t>
+          <t>0,41; 3,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,1</t>
+          <t>-1,11; 3,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,92</t>
+          <t>-0,19; 4,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,57</t>
+          <t>-2,99; 3,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,29</t>
+          <t>-0,34; 2,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,14</t>
+          <t>0,56; 3,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,08</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 91,54</t>
+          <t>-28,68; 92,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 134,78</t>
+          <t>-10,33; 125,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 162,69</t>
+          <t>10,97; 160,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 97,12</t>
+          <t>-19,86; 96,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 122,91</t>
+          <t>-3,16; 115,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 84,19</t>
+          <t>-43,55; 78,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 78,16</t>
+          <t>-8,23; 76,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,62; 107,1</t>
+          <t>12,79; 100,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 98,43</t>
+          <t>3,12; 99,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,03</t>
+          <t>-4,07; 1,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,89</t>
+          <t>-2,49; 2,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,7</t>
+          <t>-0,73; 5,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,64</t>
+          <t>-1,29; 4,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,94</t>
+          <t>1,53; 7,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 7,03</t>
+          <t>0,19; 7,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,5</t>
+          <t>-1,85; 2,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,51</t>
+          <t>0,31; 4,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,7</t>
+          <t>0,89; 5,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,31; 43,71</t>
+          <t>-70,43; 54,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,09; 130,11</t>
+          <t>-43,65; 102,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 222,57</t>
+          <t>-15,85; 213,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 85,8</t>
+          <t>-15,15; 90,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,95; 149,6</t>
+          <t>16,25; 148,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,85; 131,38</t>
+          <t>3,29; 148,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 55,61</t>
+          <t>-25,35; 54,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,6; 94,91</t>
+          <t>3,58; 108,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,84; 121,24</t>
+          <t>13,11; 121,85</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,56</t>
+          <t>-2,12; 2,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,18</t>
+          <t>-1,9; 2,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,68</t>
+          <t>-1,19; 4,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,93</t>
+          <t>-0,14; 3,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,07</t>
+          <t>-0,29; 4,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,12</t>
+          <t>2,75; 7,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,31</t>
+          <t>-0,14; 3,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,3</t>
+          <t>-0,41; 3,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,74</t>
+          <t>1,91; 5,62</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-87,87; 475,94</t>
+          <t>-83,41; 456,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,6; 764,2</t>
+          <t>-66,9; 920,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 83,69</t>
+          <t>-2,49; 88,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 86,07</t>
+          <t>-4,43; 85,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38,59; 144,1</t>
+          <t>42,94; 160,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 81,33</t>
+          <t>-4,29; 80,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 82,59</t>
+          <t>-9,15; 79,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>40,38; 141,94</t>
+          <t>31,55; 137,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,54</t>
+          <t>-0,11; 1,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,84</t>
+          <t>0,08; 1,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,43</t>
+          <t>0,39; 2,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,95</t>
+          <t>0,65; 2,98</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,56</t>
+          <t>1,17; 3,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,0</t>
+          <t>0,88; 3,82</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,03</t>
+          <t>0,6; 2,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,37</t>
+          <t>0,93; 2,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,97</t>
+          <t>1,15; 2,9</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 68,05</t>
+          <t>-5,68; 68,08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,1; 80,97</t>
+          <t>1,63; 76,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15,69; 108,84</t>
+          <t>15,2; 112,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,0; 63,06</t>
+          <t>10,89; 63,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,3; 74,98</t>
+          <t>20,62; 76,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,57; 84,85</t>
+          <t>17,51; 80,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,0; 56,82</t>
+          <t>13,77; 57,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,99; 65,28</t>
+          <t>20,92; 66,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,01; 81,82</t>
+          <t>27,54; 78,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,86</t>
+          <t>-2,39; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,67</t>
+          <t>-1,37; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,64</t>
+          <t>-1,87; 2,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,62</t>
+          <t>-3,12; 2,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,19</t>
+          <t>-3,2; 2,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,57</t>
+          <t>-3,03; 1,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,85</t>
+          <t>-1,83; 2,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,32</t>
+          <t>-1,6; 2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,59</t>
+          <t>-1,9; 1,51</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-17,71%</t>
+          <t>-14,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-0,74%</t>
+          <t>-1,65%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 133,04</t>
+          <t>-58,87; 126,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 175,8</t>
+          <t>-36,85; 195,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 131,3</t>
+          <t>-45,37; 118,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 122,32</t>
+          <t>-64,08; 136,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 117,66</t>
+          <t>-63,38; 114,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,73; 79,34</t>
+          <t>-57,52; 91,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,27; 74,44</t>
+          <t>-44,68; 83,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 89,65</t>
+          <t>-38,95; 89,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 67,39</t>
+          <t>-43,37; 61,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>1,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,29</t>
+          <t>0,24; 5,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,71</t>
+          <t>-0,64; 3,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,78</t>
+          <t>-0,42; 3,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,8</t>
+          <t>-1,84; 4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,23</t>
+          <t>-2,91; 3,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,85</t>
+          <t>-1,08; 4,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 3,85</t>
+          <t>-0,12; 3,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,55</t>
+          <t>-0,95; 2,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,65</t>
+          <t>0,21; 3,53</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115,67%</t>
+          <t>107,32%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 863,33</t>
+          <t>-20,12; 836,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 596,56</t>
+          <t>-43,02; 527,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 780,63</t>
+          <t>-33,63; 586,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 175,54</t>
+          <t>-40,05; 163,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,42; 116,0</t>
+          <t>-56,43; 107,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 179,61</t>
+          <t>-21,66; 183,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 197,18</t>
+          <t>-6,07; 202,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 134,69</t>
+          <t>-29,72; 133,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 202,11</t>
+          <t>-0,27; 185,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>4,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,56</t>
+          <t>-0,19; 4,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,32</t>
+          <t>-1,49; 2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,71</t>
+          <t>0,92; 6,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,8</t>
+          <t>0,12; 10,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 10,25</t>
+          <t>-0,93; 9,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 10,56</t>
+          <t>1,07; 10,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,32</t>
+          <t>1,04; 5,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,13</t>
+          <t>-0,53; 3,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,37</t>
+          <t>2,02; 6,5</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>130,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>124,54%</t>
+          <t>123,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>135,29%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 271,73</t>
+          <t>-8,92; 249,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 140,56</t>
+          <t>-47,24; 152,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 219,03</t>
+          <t>13,79; 351,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 405,45</t>
+          <t>-8,91; 413,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 426,91</t>
+          <t>-20,48; 386,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 441,95</t>
+          <t>5,78; 409,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,69; 240,06</t>
+          <t>22,58; 225,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 136,45</t>
+          <t>-15,55; 154,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 212,76</t>
+          <t>48,28; 292,2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>2,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,88</t>
+          <t>-0,84; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,64</t>
+          <t>-0,3; 2,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,18</t>
+          <t>0,34; 3,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,98</t>
+          <t>-0,8; 3,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,91</t>
+          <t>-0,03; 4,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 3,6</t>
+          <t>0,29; 4,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,34</t>
+          <t>-0,37; 2,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,07</t>
+          <t>0,41; 3,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>1,08; 3,49</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 92,72</t>
+          <t>-26,52; 93,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 125,44</t>
+          <t>-10,9; 119,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,97; 160,0</t>
+          <t>7,89; 157,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 96,17</t>
+          <t>-13,03; 94,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 115,52</t>
+          <t>-3,85; 111,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 78,85</t>
+          <t>3,68; 111,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 76,61</t>
+          <t>-9,77; 77,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,79; 100,1</t>
+          <t>9,43; 102,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 99,11</t>
+          <t>26,6; 122,74</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,25</t>
+          <t>-3,81; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,69</t>
+          <t>-2,25; 2,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,22</t>
+          <t>-1,18; 4,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,67</t>
+          <t>-1,44; 4,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,77</t>
+          <t>1,49; 7,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 7,37</t>
+          <t>1,45; 6,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,46</t>
+          <t>-1,59; 2,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,81</t>
+          <t>0,22; 4,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,58</t>
+          <t>0,98; 5,03</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 54,43</t>
+          <t>-65,25; 52,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,65; 102,33</t>
+          <t>-42,31; 128,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 213,7</t>
+          <t>-23,53; 193,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 90,62</t>
+          <t>-17,87; 92,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,25; 148,49</t>
+          <t>16,21; 143,76</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,29; 148,21</t>
+          <t>16,2; 136,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 54,72</t>
+          <t>-23,38; 52,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,58; 108,61</t>
+          <t>3,74; 101,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,11; 121,85</t>
+          <t>14,01; 109,17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>3,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,44</t>
+          <t>-2,17; 2,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,5</t>
+          <t>-2,12; 2,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,39</t>
+          <t>-0,9; 4,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,98</t>
+          <t>-0,17; 4,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,06</t>
+          <t>-0,01; 4,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,14</t>
+          <t>2,51; 6,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,3</t>
+          <t>-0,25; 3,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,23</t>
+          <t>-0,19; 3,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,62</t>
+          <t>2,06; 5,85</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-83,41; 456,86</t>
+          <t>-82,52; 420,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,9; 920,24</t>
+          <t>-71,48; 830,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 88,93</t>
+          <t>-2,73; 89,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 85,63</t>
+          <t>-0,9; 90,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42,94; 160,29</t>
+          <t>36,92; 147,69</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 80,03</t>
+          <t>-4,5; 84,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 79,69</t>
+          <t>-3,84; 82,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31,55; 137,59</t>
+          <t>37,27; 145,33</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,56</t>
+          <t>-0,09; 1,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,71</t>
+          <t>0,03; 1,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,52</t>
+          <t>0,87; 2,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,98</t>
+          <t>0,69; 3,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,61</t>
+          <t>1,12; 3,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,82</t>
+          <t>2,1; 4,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,08</t>
+          <t>0,5; 2,05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,44</t>
+          <t>0,92; 2,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,9</t>
+          <t>1,72; 3,2</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 68,08</t>
+          <t>-3,12; 73,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1,63; 76,14</t>
+          <t>-0,47; 76,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15,2; 112,54</t>
+          <t>28,78; 121,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,89; 63,79</t>
+          <t>11,97; 66,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,62; 76,95</t>
+          <t>17,9; 74,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,51; 80,34</t>
+          <t>34,95; 89,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,77; 57,67</t>
+          <t>10,99; 56,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,92; 66,39</t>
+          <t>21,25; 65,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>27,54; 78,68</t>
+          <t>39,49; 89,04</t>
         </is>
       </c>
     </row>
